--- a/automated_test/DAST_Security_Report_LegalRiskAnalyzer_2026-06-10T08-19-17.xlsx
+++ b/automated_test/DAST_Security_Report_LegalRiskAnalyzer_2026-06-10T08-19-17.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PDD App\automated_test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4766412-8D31-41D7-90C8-A424C5D8BD3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF413DC-BCA5-494B-B7BD-9E561EA4B25B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -715,7 +715,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,6 +757,13 @@
       <sz val="11"/>
       <color rgb="FFFF9966"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -824,7 +831,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -855,6 +862,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1698,7 +1708,7 @@
       <c r="K2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="12" t="s">
         <v>55</v>
       </c>
     </row>
